--- a/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
+++ b/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
@@ -1,21 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Comparison Analysis/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_6C7BFDCE8F79A8D366075C52F3D12AB2DFF4D2D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{952E08A7-2ECD-4110-8230-5D8057989E92}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Non-User</t>
+  </si>
+  <si>
+    <t>Not in OMOP</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Not in Source</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +105,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +157,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +191,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +226,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,160 +402,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>OMOP</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Freq</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>335</v>
       </c>
       <c r="C2">
-        <v>262</v>
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>36</v>
+      </c>
+      <c r="E2">
+        <f>SUM(B2:D2)</f>
+        <v>384</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Not in Source</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>326</v>
+      </c>
+      <c r="E3">
+        <f>SUM(B3:D3)</f>
+        <v>337</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>386</v>
       </c>
       <c r="C4">
-        <v>363</v>
+        <v>1108</v>
+      </c>
+      <c r="D4">
+        <v>22862</v>
+      </c>
+      <c r="E4">
+        <f>SUM(B4:D4)</f>
+        <v>24356</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not in OMOP</t>
-        </is>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>732</v>
       </c>
       <c r="C5">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Not in Source</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not in OMOP</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not in OMOP</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Not in Source</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>22862</v>
+        <f t="shared" ref="C5:E5" si="0">SUM(C2:C4)</f>
+        <v>1121</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>23224</v>
       </c>
     </row>
   </sheetData>

--- a/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
+++ b/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
@@ -1,63 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Comparison Analysis/Results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_6C7BFDCE8F79A8D366075C52F3D12AB2DFF4D2D2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{952E08A7-2ECD-4110-8230-5D8057989E92}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Non-User</t>
-  </si>
-  <si>
-    <t>Not in OMOP</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Not in Source</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -191,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -226,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -402,30 +350,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Non-User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Not in OMOP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Non-User</t>
+        </is>
       </c>
       <c r="B2">
         <v>335</v>
@@ -436,14 +391,12 @@
       <c r="D2">
         <v>36</v>
       </c>
-      <c r="E2">
-        <f>SUM(B2:D2)</f>
-        <v>384</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Not in Source</t>
+        </is>
       </c>
       <c r="B3">
         <v>11</v>
@@ -454,14 +407,12 @@
       <c r="D3">
         <v>326</v>
       </c>
-      <c r="E3">
-        <f>SUM(B3:D3)</f>
-        <v>337</v>
-      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
       </c>
       <c r="B4">
         <v>386</v>
@@ -471,27 +422,6 @@
       </c>
       <c r="D4">
         <v>22862</v>
-      </c>
-      <c r="E4">
-        <f>SUM(B4:D4)</f>
-        <v>24356</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <f>SUM(B2:B4)</f>
-        <v>732</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:E5" si="0">SUM(C2:C4)</f>
-        <v>1121</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>23224</v>
       </c>
     </row>
   </sheetData>

--- a/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
+++ b/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
@@ -1,21 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Comparison Analysis/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_EC7EFDCE8F79A8D366075C52F315523247B7A157" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3BBED88-2D9A-4844-9472-9620DC19ADBC}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView minimized="1" xWindow="5952" yWindow="5952" windowWidth="11556" windowHeight="6144" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Non-User</t>
+  </si>
+  <si>
+    <t>Not in OMOP</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Not in Source</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +89,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +141,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +175,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +210,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,53 +386,44 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Not in OMOP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>335</v>
+        <v>424</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Not in Source</t>
-        </is>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>11</v>
@@ -405,23 +432,21 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>326</v>
+        <v>268</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>386</v>
+        <v>292</v>
       </c>
       <c r="C4">
-        <v>1108</v>
+        <v>695</v>
       </c>
       <c r="D4">
-        <v>22862</v>
+        <v>16652</v>
       </c>
     </row>
   </sheetData>

--- a/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
+++ b/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Comparison Analysis/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EC7EFDCE8F79A8D366075C52F315523247B7A157" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3BBED88-2D9A-4844-9472-9620DC19ADBC}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_EC7EFDCE8F79A8D366075C52F315523247B7A157" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1650D4DD-3CFA-4C65-BFEA-6DCCDA9DFC7B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5952" yWindow="5952" windowWidth="11556" windowHeight="6144" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>Source</t>
   </si>
@@ -35,6 +48,9 @@
   </si>
   <si>
     <t>Not in Source</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -387,13 +403,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -406,8 +422,11 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -420,8 +439,12 @@
       <c r="D2">
         <v>58</v>
       </c>
+      <c r="E2">
+        <f>SUM(B2:D2)</f>
+        <v>494</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -434,8 +457,12 @@
       <c r="D3">
         <v>268</v>
       </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E4" si="0">SUM(B3:D3)</f>
+        <v>279</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -447,6 +474,27 @@
       </c>
       <c r="D4">
         <v>16652</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>17639</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>727</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:D5" si="1">SUM(C2:C4)</f>
+        <v>707</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>16978</v>
       </c>
     </row>
   </sheetData>

--- a/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
+++ b/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
@@ -1,63 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Comparison Analysis/Results/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_EC7EFDCE8F79A8D366075C52F315523247B7A157" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1650D4DD-3CFA-4C65-BFEA-6DCCDA9DFC7B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Non-User</t>
-  </si>
-  <si>
-    <t>Not in OMOP</t>
-  </si>
-  <si>
-    <t>User</t>
-  </si>
-  <si>
-    <t>Not in Source</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -157,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -191,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -226,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -402,51 +350,53 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>5</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Non-User</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Not in OMOP</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Non-User</t>
+        </is>
       </c>
       <c r="B2">
-        <v>424</v>
+        <v>710</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>58</v>
-      </c>
-      <c r="E2">
-        <f>SUM(B2:D2)</f>
-        <v>494</v>
+        <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>4</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Not in Source</t>
+        </is>
       </c>
       <c r="B3">
         <v>11</v>
@@ -457,44 +407,21 @@
       <c r="D3">
         <v>268</v>
       </c>
-      <c r="E3">
-        <f t="shared" ref="E3:E4" si="0">SUM(B3:D3)</f>
-        <v>279</v>
-      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
       </c>
       <c r="B4">
-        <v>292</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="D4">
-        <v>16652</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>17639</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <f>SUM(B2:B4)</f>
-        <v>727</v>
-      </c>
-      <c r="C5">
-        <f t="shared" ref="C5:D5" si="1">SUM(C2:C4)</f>
-        <v>707</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="1"/>
-        <v>16978</v>
+        <v>16623</v>
       </c>
     </row>
   </sheetData>

--- a/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
+++ b/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
@@ -1,21 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Comparison Analysis/Results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_0D64FDCE8F79A8D366075C52F3977A33A3E0B3B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23E57F57-35A8-44B4-B9C0-12C035626A1B}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Non-User</t>
+  </si>
+  <si>
+    <t>Not in OMOP</t>
+  </si>
+  <si>
+    <t>User</t>
+  </si>
+  <si>
+    <t>Not in Source</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +105,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +157,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +191,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +226,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,78 +402,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Not in OMOP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Non-User</t>
-        </is>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
       </c>
       <c r="B2">
-        <v>710</v>
+        <v>613</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D2">
-        <v>87</v>
+        <v>69</v>
+      </c>
+      <c r="E2">
+        <f>SUM(B2:D2)</f>
+        <v>699</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Not in Source</t>
-        </is>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>268</v>
+        <v>321</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E4" si="0">SUM(B3:D3)</f>
+        <v>329</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>User</t>
-        </is>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>682</v>
+        <v>518</v>
       </c>
       <c r="D4">
-        <v>16623</v>
+        <v>21889</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>22407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v>621</v>
+      </c>
+      <c r="C5">
+        <f t="shared" ref="C5:D5" si="1">SUM(C2:C4)</f>
+        <v>535</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>22279</v>
       </c>
     </row>
   </sheetData>

--- a/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
+++ b/Comparison Analysis/Results/contigency_table_for_user_status.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/orms1149_ox_ac_uk/Documents/Documents/GitHub/OMOP-Validation-Study/Comparison Analysis/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_0D64FDCE8F79A8D366075C52F3977A33A3E0B3B2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23E57F57-35A8-44B4-B9C0-12C035626A1B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_2E6EFDCE8F79A8D366075C52F3A962F18210D080" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677266FD-E572-4993-AECA-6E9E69DA10C6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,17 +428,17 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>613</v>
+        <v>492</v>
       </c>
       <c r="C2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="E2">
         <f>SUM(B2:D2)</f>
-        <v>699</v>
+        <v>545</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -446,7 +446,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>107</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -456,7 +456,7 @@
       </c>
       <c r="E3">
         <f t="shared" ref="E3:E4" si="0">SUM(B3:D3)</f>
-        <v>329</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -467,14 +467,14 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D4">
-        <v>21889</v>
+        <v>21943</v>
       </c>
       <c r="E4">
         <f t="shared" si="0"/>
-        <v>22407</v>
+        <v>22462</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -483,7 +483,7 @@
       </c>
       <c r="B5">
         <f>SUM(B2:B4)</f>
-        <v>621</v>
+        <v>599</v>
       </c>
       <c r="C5">
         <f t="shared" ref="C5:D5" si="1">SUM(C2:C4)</f>
@@ -491,7 +491,7 @@
       </c>
       <c r="D5">
         <f t="shared" si="1"/>
-        <v>22279</v>
+        <v>22301</v>
       </c>
     </row>
   </sheetData>
